--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f.wichelmann\Desktop\Community App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8CDD83-A9A5-47A3-9151-EFFDA480A1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701D5B70-D216-4D86-AFBB-EE688AD45008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36150" yWindow="945" windowWidth="20130" windowHeight="19575" xr2:uid="{1867976E-48FD-415F-AB5D-37265D2F407F}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="18000" windowHeight="11250" xr2:uid="{1867976E-48FD-415F-AB5D-37265D2F407F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -37,19 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
-  <si>
-    <t>Max Mustermann</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Test FW</t>
-  </si>
-  <si>
-    <t>fwichelmann@googlemail.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>Silbersteinstraße</t>
   </si>
@@ -87,41 +75,62 @@
     <t>rolle</t>
   </si>
   <si>
-    <t>max@silber.de</t>
-  </si>
-  <si>
     <t>Sil-101</t>
   </si>
   <si>
-    <t>Erika Muster</t>
-  </si>
-  <si>
-    <t>erika@wilhelm.de</t>
-  </si>
-  <si>
-    <t>Sil-102</t>
-  </si>
-  <si>
-    <t>Sil-103</t>
-  </si>
-  <si>
-    <t>Sil-104</t>
-  </si>
-  <si>
-    <t>Wilh-101</t>
-  </si>
-  <si>
-    <t>Wilh-102</t>
-  </si>
-  <si>
-    <t>XY</t>
+    <t>Max Mieter</t>
+  </si>
+  <si>
+    <t>max@web.de</t>
+  </si>
+  <si>
+    <t>Hakan Hausmeister</t>
+  </si>
+  <si>
+    <t>hakan@nena.de</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>hausmeister</t>
+  </si>
+  <si>
+    <t>Wilma Wilhelm</t>
+  </si>
+  <si>
+    <t>wilma@gmx.de</t>
+  </si>
+  <si>
+    <t>Wilh-202</t>
+  </si>
+  <si>
+    <t>Heiko Hausmeister</t>
+  </si>
+  <si>
+    <t>heiko@nena.de</t>
+  </si>
+  <si>
+    <t>Clara Cleaner</t>
+  </si>
+  <si>
+    <t>clara@service.de</t>
+  </si>
+  <si>
+    <t>Clean-Team</t>
+  </si>
+  <si>
+    <t>cleaner</t>
+  </si>
+  <si>
+    <t>Alle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,13 +153,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0A0A0A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -158,18 +160,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="7"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
+      <sz val="7"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -199,25 +200,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -535,156 +533,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A279333C-0DB1-40B1-8A0C-2A43C1ECE92C}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="21.42578125" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="22.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="21.453125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>8</v>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{3549A2EA-E63D-43C8-9FBA-88FF4B6758E9}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{26B35353-91E9-48B4-84D5-60BE886959CF}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{5C346C9D-812B-4D16-9C8A-F5B4476B7D3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>